--- a/output/roomself_excel/8685.xlsx
+++ b/output/roomself_excel/8685.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,16 +470,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>500842</v>
+        <v>289789</v>
       </c>
       <c r="D2" t="n">
-        <v>8088</v>
+        <v>4860</v>
       </c>
       <c r="E2" t="n">
-        <v>968</v>
+        <v>614</v>
       </c>
       <c r="F2" t="n">
-        <v>959</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>460829</v>
+        <v>98899</v>
       </c>
       <c r="D3" t="n">
-        <v>9468</v>
+        <v>2552</v>
       </c>
       <c r="E3" t="n">
-        <v>969</v>
+        <v>443</v>
       </c>
       <c r="F3" t="n">
-        <v>658</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>98899</v>
+        <v>139895</v>
       </c>
       <c r="D4" t="n">
-        <v>2552</v>
+        <v>3160</v>
       </c>
       <c r="E4" t="n">
-        <v>664</v>
+        <v>595</v>
       </c>
       <c r="F4" t="n">
-        <v>309</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5">
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>139895</v>
+        <v>96940</v>
       </c>
       <c r="D5" t="n">
-        <v>3160</v>
+        <v>2528</v>
       </c>
       <c r="E5" t="n">
-        <v>969</v>
+        <v>442</v>
       </c>
       <c r="F5" t="n">
-        <v>324</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>96940</v>
+        <v>41944</v>
       </c>
       <c r="D6" t="n">
-        <v>2528</v>
+        <v>1640</v>
       </c>
       <c r="E6" t="n">
-        <v>442</v>
+        <v>253</v>
       </c>
       <c r="F6" t="n">
-        <v>294</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>35886</v>
+        <v>460829</v>
       </c>
       <c r="D7" t="n">
-        <v>1752</v>
+        <v>9468</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>969</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>658</v>
       </c>
     </row>
     <row r="8">
@@ -602,16 +602,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12614</v>
+        <v>614</v>
       </c>
       <c r="D8" t="n">
-        <v>900</v>
+        <v>698</v>
       </c>
       <c r="E8" t="n">
-        <v>106</v>
+        <v>211</v>
       </c>
       <c r="F8" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
@@ -624,16 +624,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>50046</v>
+        <v>149161</v>
       </c>
       <c r="D9" t="n">
-        <v>2168</v>
+        <v>3296</v>
       </c>
       <c r="E9" t="n">
-        <v>323</v>
+        <v>604</v>
       </c>
       <c r="F9" t="n">
-        <v>198</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>41944</v>
+        <v>61278</v>
       </c>
       <c r="D10" t="n">
-        <v>1640</v>
+        <v>2016</v>
       </c>
       <c r="E10" t="n">
-        <v>253</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -668,16 +668,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22080</v>
+        <v>35886</v>
       </c>
       <c r="D11" t="n">
-        <v>1192</v>
+        <v>1752</v>
       </c>
       <c r="E11" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -690,15 +690,81 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>12614</v>
+      </c>
+      <c r="D12" t="n">
+        <v>900</v>
+      </c>
+      <c r="E12" t="n">
+        <v>106</v>
+      </c>
+      <c r="F12" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>50046</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2168</v>
+      </c>
+      <c r="E13" t="n">
+        <v>323</v>
+      </c>
+      <c r="F13" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>22080</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1192</v>
+      </c>
+      <c r="E14" t="n">
+        <v>177</v>
+      </c>
+      <c r="F14" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
         <v>21600</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D15" t="n">
         <v>1180</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E15" t="n">
         <v>135</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F15" t="n">
         <v>39</v>
       </c>
     </row>

--- a/output/roomself_excel/8685.xlsx
+++ b/output/roomself_excel/8685.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,77 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_5</t>
         </is>
       </c>
     </row>
@@ -475,12 +540,37 @@
       <c r="D2" t="n">
         <v>4860</v>
       </c>
-      <c r="E2" t="n">
-        <v>614</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>221</v>
-      </c>
+        <v>575</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>182</v>
+      </c>
+      <c r="J2" t="n">
+        <v>39</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +587,37 @@
       <c r="D3" t="n">
         <v>2552</v>
       </c>
-      <c r="E3" t="n">
-        <v>443</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>295</v>
-      </c>
+        <v>509</v>
+      </c>
+      <c r="G3" t="n">
+        <v>39</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>365</v>
+      </c>
+      <c r="J3" t="n">
+        <v>39</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +634,45 @@
       <c r="D4" t="n">
         <v>3160</v>
       </c>
-      <c r="E4" t="n">
-        <v>595</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>324</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="G4" t="n">
+        <v>34</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>521</v>
+      </c>
+      <c r="J4" t="n">
+        <v>38</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>249</v>
+      </c>
+      <c r="M4" t="n">
+        <v>39</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +689,45 @@
       <c r="D5" t="n">
         <v>2528</v>
       </c>
-      <c r="E5" t="n">
-        <v>442</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>294</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="G5" t="n">
+        <v>33</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>370</v>
+      </c>
+      <c r="J5" t="n">
+        <v>38</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>256</v>
+      </c>
+      <c r="M5" t="n">
+        <v>39</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +744,37 @@
       <c r="D6" t="n">
         <v>1640</v>
       </c>
-      <c r="E6" t="n">
-        <v>253</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>235</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="G6" t="n">
+        <v>39</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>196</v>
+      </c>
+      <c r="J6" t="n">
+        <v>39</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,11 +791,60 @@
       <c r="D7" t="n">
         <v>9468</v>
       </c>
-      <c r="E7" t="n">
-        <v>969</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>658</v>
+        <v>581</v>
+      </c>
+      <c r="G7" t="n">
+        <v>35</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>177</v>
+      </c>
+      <c r="J7" t="n">
+        <v>35</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>186</v>
+      </c>
+      <c r="M7" t="n">
+        <v>33</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>159</v>
+      </c>
+      <c r="P7" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>367</v>
+      </c>
+      <c r="S7" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="8">
@@ -607,12 +862,29 @@
       <c r="D8" t="n">
         <v>698</v>
       </c>
-      <c r="E8" t="n">
-        <v>211</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>47</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="G8" t="n">
+        <v>41</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +901,45 @@
       <c r="D9" t="n">
         <v>3296</v>
       </c>
-      <c r="E9" t="n">
-        <v>604</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>298</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="G9" t="n">
+        <v>41</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>495</v>
+      </c>
+      <c r="J9" t="n">
+        <v>38</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>253</v>
+      </c>
+      <c r="M9" t="n">
+        <v>39</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +956,21 @@
       <c r="D10" t="n">
         <v>2016</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +987,21 @@
       <c r="D11" t="n">
         <v>1752</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +1018,29 @@
       <c r="D12" t="n">
         <v>900</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>106</v>
       </c>
-      <c r="F12" t="n">
-        <v>39</v>
-      </c>
+      <c r="G12" t="n">
+        <v>39</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +1057,37 @@
       <c r="D13" t="n">
         <v>2168</v>
       </c>
-      <c r="E13" t="n">
-        <v>323</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>183</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="G13" t="n">
+        <v>39</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>258</v>
+      </c>
+      <c r="J13" t="n">
+        <v>39</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +1104,37 @@
       <c r="D14" t="n">
         <v>1192</v>
       </c>
-      <c r="E14" t="n">
-        <v>177</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>153</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="G14" t="n">
+        <v>39</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>121</v>
+      </c>
+      <c r="J14" t="n">
+        <v>39</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +1151,29 @@
       <c r="D15" t="n">
         <v>1180</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>135</v>
       </c>
-      <c r="F15" t="n">
-        <v>39</v>
-      </c>
+      <c r="G15" t="n">
+        <v>39</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/8685.xlsx
+++ b/output/roomself_excel/8685.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:AQ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,6 +522,126 @@
       <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ExtWallWidth_5</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_3</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_3</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_3</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_3</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_4</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_4</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_4</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_4</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_5</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_5</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_5</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_5</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_6</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_6</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_6</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_6</t>
         </is>
       </c>
     </row>
@@ -571,6 +691,54 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>371</v>
+      </c>
+      <c r="W2" t="n">
+        <v>39</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Z2" t="n">
+        <v>93</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>39</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -618,6 +786,42 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>187</v>
+      </c>
+      <c r="W3" t="n">
+        <v>39</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -673,6 +877,78 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>190</v>
+      </c>
+      <c r="W4" t="n">
+        <v>34</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Z4" t="n">
+        <v>96</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>91</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>94</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>39</v>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -728,6 +1004,42 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>261</v>
+      </c>
+      <c r="W5" t="n">
+        <v>38</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -775,6 +1087,30 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -846,6 +1182,54 @@
       <c r="S7" t="n">
         <v>39</v>
       </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>377</v>
+      </c>
+      <c r="W7" t="n">
+        <v>35</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Z7" t="n">
+        <v>219</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>39</v>
+      </c>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -885,6 +1269,42 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>57</v>
+      </c>
+      <c r="W8" t="n">
+        <v>41</v>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -940,6 +1360,102 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>190</v>
+      </c>
+      <c r="W9" t="n">
+        <v>41</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Z9" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AD9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>88</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AL9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AP9" t="n">
+        <v>94</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -971,6 +1487,30 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1002,6 +1542,30 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1041,6 +1605,30 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1088,6 +1676,54 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>87</v>
+      </c>
+      <c r="W13" t="n">
+        <v>39</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Z13" t="n">
+        <v>66</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>39</v>
+      </c>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1135,6 +1771,42 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>65</v>
+      </c>
+      <c r="W14" t="n">
+        <v>39</v>
+      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1174,6 +1846,42 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>105</v>
+      </c>
+      <c r="W15" t="n">
+        <v>39</v>
+      </c>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
